--- a/DateBase/orders/Nha Thu_2026-6-3.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-3.xlsx
@@ -915,6 +915,9 @@
       <c r="G2" t="str">
         <v>01520255153054030253031275101515102555156059201017105101110141561012331510101010103101010</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
